--- a/artfynd/A 27461-2022 artfynd.xlsx
+++ b/artfynd/A 27461-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568925</v>
       </c>
       <c r="B2" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568924</v>
       </c>
       <c r="B3" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135568926</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135568927</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135568929</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135568931</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>135568932</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135568933</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>135568937</v>
       </c>
       <c r="B10" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>135568938</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27461-2022 artfynd.xlsx
+++ b/artfynd/A 27461-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568925</v>
       </c>
       <c r="B2" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568924</v>
       </c>
       <c r="B3" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135568926</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135568927</v>
       </c>
       <c r="B5" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135568929</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135568931</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>135568932</v>
       </c>
       <c r="B8" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135568933</v>
       </c>
       <c r="B9" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>135568937</v>
       </c>
       <c r="B10" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>135568938</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27461-2022 artfynd.xlsx
+++ b/artfynd/A 27461-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568925</v>
       </c>
       <c r="B2" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568924</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135568926</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135568927</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135568929</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135568931</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>135568932</v>
       </c>
       <c r="B8" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135568933</v>
       </c>
       <c r="B9" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>135568937</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>135568938</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27461-2022 artfynd.xlsx
+++ b/artfynd/A 27461-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568925</v>
       </c>
       <c r="B2" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568924</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135568926</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135568927</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135568929</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135568931</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>135568932</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135568933</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>135568937</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>135568938</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27461-2022 artfynd.xlsx
+++ b/artfynd/A 27461-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568925</v>
       </c>
       <c r="B2" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568924</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135568926</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135568927</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135568929</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135568931</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>135568932</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135568933</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>135568937</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>135568938</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27461-2022 artfynd.xlsx
+++ b/artfynd/A 27461-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568925</v>
       </c>
       <c r="B2" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568924</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135568926</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135568927</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>135568929</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135568931</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>135568932</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135568933</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>135568937</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>135568938</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
